--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/208.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/208.xlsx
@@ -426,13 +426,13 @@
         <v>-2.541864521806066</v>
       </c>
       <c r="E2">
-        <v>-16.07658746455222</v>
+        <v>-17.86380407336742</v>
       </c>
       <c r="F2">
-        <v>-2.73867638641919</v>
+        <v>-2.963242647481122</v>
       </c>
       <c r="G2">
-        <v>-10.56103206531705</v>
+        <v>-12.05013862270001</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.542530642709449</v>
       </c>
       <c r="E3">
-        <v>-18.22284866353957</v>
+        <v>-19.31205987423449</v>
       </c>
       <c r="F3">
-        <v>-3.132118596420246</v>
+        <v>-2.627902127112423</v>
       </c>
       <c r="G3">
-        <v>-10.06593335882797</v>
+        <v>-12.68903418523288</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.444788834746975</v>
       </c>
       <c r="E4">
-        <v>-17.01143658174767</v>
+        <v>-19.65547670060617</v>
       </c>
       <c r="F4">
-        <v>-3.003132679762932</v>
+        <v>-2.77152115394019</v>
       </c>
       <c r="G4">
-        <v>-10.54333388886411</v>
+        <v>-12.46096739248695</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.240592984188636</v>
       </c>
       <c r="E5">
-        <v>-18.60433184241973</v>
+        <v>-18.86834640554092</v>
       </c>
       <c r="F5">
-        <v>-2.697751723251283</v>
+        <v>-2.570305741595774</v>
       </c>
       <c r="G5">
-        <v>-11.03258948247638</v>
+        <v>-11.86055692184811</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-1.933775418250697</v>
       </c>
       <c r="E6">
-        <v>-17.53235600379801</v>
+        <v>-20.60128019642617</v>
       </c>
       <c r="F6">
-        <v>-3.074420321713052</v>
+        <v>-2.670443763450594</v>
       </c>
       <c r="G6">
-        <v>-10.53058828853792</v>
+        <v>-11.71533653122244</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.533722588662818</v>
       </c>
       <c r="E7">
-        <v>-18.76224425954121</v>
+        <v>-20.75748537884676</v>
       </c>
       <c r="F7">
-        <v>-2.166296048637204</v>
+        <v>-2.832389590697898</v>
       </c>
       <c r="G7">
-        <v>-8.807369882254321</v>
+        <v>-10.89697298446014</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.052035065615359</v>
       </c>
       <c r="E8">
-        <v>-21.02006441570752</v>
+        <v>-21.45506057193631</v>
       </c>
       <c r="F8">
-        <v>-3.093610280966305</v>
+        <v>-2.493772877251127</v>
       </c>
       <c r="G8">
-        <v>-9.323606422011652</v>
+        <v>-10.78201429060895</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.5085822988949473</v>
       </c>
       <c r="E9">
-        <v>-21.16919159325411</v>
+        <v>-22.58976936098629</v>
       </c>
       <c r="F9">
-        <v>-3.617613134057397</v>
+        <v>-2.582286419342462</v>
       </c>
       <c r="G9">
-        <v>-7.453300477418238</v>
+        <v>-9.955033393807925</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.07847289240131453</v>
       </c>
       <c r="E10">
-        <v>-21.2591044446764</v>
+        <v>-23.14219337670799</v>
       </c>
       <c r="F10">
-        <v>-2.616794548608284</v>
+        <v>-2.850625270703126</v>
       </c>
       <c r="G10">
-        <v>-8.107745672349063</v>
+        <v>-9.297343864248614</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.6892225027203387</v>
       </c>
       <c r="E11">
-        <v>-21.81748793219219</v>
+        <v>-23.64328713955274</v>
       </c>
       <c r="F11">
-        <v>-3.456839446685055</v>
+        <v>-2.786270235547035</v>
       </c>
       <c r="G11">
-        <v>-7.360247663400404</v>
+        <v>-8.80905826047935</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.299524723352736</v>
       </c>
       <c r="E12">
-        <v>-23.09891927909069</v>
+        <v>-24.23457451920827</v>
       </c>
       <c r="F12">
-        <v>-3.240310834532486</v>
+        <v>-2.787207119079601</v>
       </c>
       <c r="G12">
-        <v>-7.500886258999723</v>
+        <v>-8.564577782949712</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>1.893585618093458</v>
       </c>
       <c r="E13">
-        <v>-22.3604700796079</v>
+        <v>-24.06601113122076</v>
       </c>
       <c r="F13">
-        <v>-3.3805111890889</v>
+        <v>-2.705946761967178</v>
       </c>
       <c r="G13">
-        <v>-7.3430924164159</v>
+        <v>-8.158585720195651</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.452718556703899</v>
       </c>
       <c r="E14">
-        <v>-25.19372342792888</v>
+        <v>-25.45066451465009</v>
       </c>
       <c r="F14">
-        <v>-3.028666276586824</v>
+        <v>-2.599517289688095</v>
       </c>
       <c r="G14">
-        <v>-4.970146342594942</v>
+        <v>-8.216109759486027</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.961058277537742</v>
       </c>
       <c r="E15">
-        <v>-26.47594725777872</v>
+        <v>-26.71305815682034</v>
       </c>
       <c r="F15">
-        <v>-2.944449476213809</v>
+        <v>-2.38856441852377</v>
       </c>
       <c r="G15">
-        <v>-5.683429863395233</v>
+        <v>-7.326907159274404</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.414324564135393</v>
       </c>
       <c r="E16">
-        <v>-25.79128274408503</v>
+        <v>-26.97423789521273</v>
       </c>
       <c r="F16">
-        <v>-3.41063062785469</v>
+        <v>-2.677560267808045</v>
       </c>
       <c r="G16">
-        <v>-5.410366135679528</v>
+        <v>-7.18224625084487</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.808487158522127</v>
       </c>
       <c r="E17">
-        <v>-27.6457834197062</v>
+        <v>-28.23474316372178</v>
       </c>
       <c r="F17">
-        <v>-2.94467147867776</v>
+        <v>-2.408104777188408</v>
       </c>
       <c r="G17">
-        <v>-3.704319529108132</v>
+        <v>-6.893811660190329</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.14528665278525</v>
       </c>
       <c r="E18">
-        <v>-25.93416968444906</v>
+        <v>-28.39647761290573</v>
       </c>
       <c r="F18">
-        <v>-1.638312890175661</v>
+        <v>-2.183933647377611</v>
       </c>
       <c r="G18">
-        <v>-3.690759534579278</v>
+        <v>-6.712029604628948</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.431264892845157</v>
       </c>
       <c r="E19">
-        <v>-29.63106416043188</v>
+        <v>-28.6669724223319</v>
       </c>
       <c r="F19">
-        <v>-2.246422370775194</v>
+        <v>-2.142594800508304</v>
       </c>
       <c r="G19">
-        <v>-4.285303718522529</v>
+        <v>-5.361105218055172</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.668586014583066</v>
       </c>
       <c r="E20">
-        <v>-29.1476699382461</v>
+        <v>-29.82687311228654</v>
       </c>
       <c r="F20">
-        <v>-2.801527934739199</v>
+        <v>-2.24390579060549</v>
       </c>
       <c r="G20">
-        <v>-3.206837229830772</v>
+        <v>-6.084078705648911</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.858650354546498</v>
       </c>
       <c r="E21">
-        <v>-30.05833021152959</v>
+        <v>-30.13916800104051</v>
       </c>
       <c r="F21">
-        <v>-2.464998707147483</v>
+        <v>-1.802872216578796</v>
       </c>
       <c r="G21">
-        <v>-4.036807549253756</v>
+        <v>-5.93695475133816</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.998750296486696</v>
       </c>
       <c r="E22">
-        <v>-30.39702383951127</v>
+        <v>-30.9932766909162</v>
       </c>
       <c r="F22">
-        <v>-1.742112295950856</v>
+        <v>-1.623529017137898</v>
       </c>
       <c r="G22">
-        <v>-2.124547061041158</v>
+        <v>-5.445183143116043</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>5.07827207871588</v>
       </c>
       <c r="E23">
-        <v>-29.65926523231465</v>
+        <v>-31.13207894772531</v>
       </c>
       <c r="F23">
-        <v>-2.16129105278949</v>
+        <v>-1.543668600936206</v>
       </c>
       <c r="G23">
-        <v>-1.773102857137667</v>
+        <v>-5.832937410494259</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.083240507615997</v>
       </c>
       <c r="E24">
-        <v>-30.91305703810733</v>
+        <v>-32.10147805736228</v>
       </c>
       <c r="F24">
-        <v>-2.623579706004615</v>
+        <v>-1.365865336497112</v>
       </c>
       <c r="G24">
-        <v>-3.012375784853983</v>
+        <v>-5.550892172730511</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.99905082327664</v>
       </c>
       <c r="E25">
-        <v>-29.71338276094331</v>
+        <v>-32.70116349206504</v>
       </c>
       <c r="F25">
-        <v>-1.840533940547076</v>
+        <v>-1.489948974864658</v>
       </c>
       <c r="G25">
-        <v>-3.548267033477967</v>
+        <v>-5.624495531705128</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.810428351295344</v>
       </c>
       <c r="E26">
-        <v>-30.75427741821338</v>
+        <v>-32.45675042868604</v>
       </c>
       <c r="F26">
-        <v>-2.272800073982539</v>
+        <v>-1.367011796982586</v>
       </c>
       <c r="G26">
-        <v>-3.034463744692</v>
+        <v>-5.49048464827543</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.50600265278208</v>
       </c>
       <c r="E27">
-        <v>-29.82518172724468</v>
+        <v>-31.84196026893071</v>
       </c>
       <c r="F27">
-        <v>-1.740992343222271</v>
+        <v>-1.339562186356019</v>
       </c>
       <c r="G27">
-        <v>-2.666437018182301</v>
+        <v>-5.589337538078068</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.083776402551548</v>
       </c>
       <c r="E28">
-        <v>-30.91886933449617</v>
+        <v>-31.75782122186819</v>
       </c>
       <c r="F28">
-        <v>-2.081564832107051</v>
+        <v>-1.301725676865749</v>
       </c>
       <c r="G28">
-        <v>-2.148786875479701</v>
+        <v>-5.799351925998353</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.546141920616806</v>
       </c>
       <c r="E29">
-        <v>-28.95770951057235</v>
+        <v>-32.22973802668153</v>
       </c>
       <c r="F29">
-        <v>-1.760273422889832</v>
+        <v>-1.172015767098388</v>
       </c>
       <c r="G29">
-        <v>-3.965769863072074</v>
+        <v>-4.998146936766098</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.906105401052017</v>
       </c>
       <c r="E30">
-        <v>-31.2689294322371</v>
+        <v>-32.07738431140447</v>
       </c>
       <c r="F30">
-        <v>-2.143070283397511</v>
+        <v>-1.214597993439297</v>
       </c>
       <c r="G30">
-        <v>-2.905835808309158</v>
+        <v>-6.662682612820572</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.186405027724976</v>
       </c>
       <c r="E31">
-        <v>-28.61398021949413</v>
+        <v>-30.52393432357623</v>
       </c>
       <c r="F31">
-        <v>-2.221259054180354</v>
+        <v>-1.608350841216403</v>
       </c>
       <c r="G31">
-        <v>-2.989357561719431</v>
+        <v>-5.80999532990711</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.408904285863114</v>
       </c>
       <c r="E32">
-        <v>-30.4129821819143</v>
+        <v>-30.33777554983191</v>
       </c>
       <c r="F32">
-        <v>-2.336230651117106</v>
+        <v>-1.352837602353284</v>
       </c>
       <c r="G32">
-        <v>-3.163435977810927</v>
+        <v>-5.890011215591294</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.6056191756366627</v>
       </c>
       <c r="E33">
-        <v>-29.14238973755316</v>
+        <v>-30.26842649887845</v>
       </c>
       <c r="F33">
-        <v>-1.932962346984042</v>
+        <v>-1.765375337723674</v>
       </c>
       <c r="G33">
-        <v>-4.376045771753953</v>
+        <v>-6.319700163315459</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.1909206015994474</v>
       </c>
       <c r="E34">
-        <v>-29.35197204310215</v>
+        <v>-30.36364898607474</v>
       </c>
       <c r="F34">
-        <v>-2.249174207287294</v>
+        <v>-1.453774170384404</v>
       </c>
       <c r="G34">
-        <v>-4.64360406223785</v>
+        <v>-6.465519762683737</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.9547416863127883</v>
       </c>
       <c r="E35">
-        <v>-28.61079670226674</v>
+        <v>-29.51185887489097</v>
       </c>
       <c r="F35">
-        <v>-1.927502577432191</v>
+        <v>-1.551229110221557</v>
       </c>
       <c r="G35">
-        <v>-4.181948486786482</v>
+        <v>-6.881337524598355</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.654884409269347</v>
       </c>
       <c r="E36">
-        <v>-26.91780405212914</v>
+        <v>-29.20630009122341</v>
       </c>
       <c r="F36">
-        <v>-1.785017585578856</v>
+        <v>-1.167437380463115</v>
       </c>
       <c r="G36">
-        <v>-4.351266338392508</v>
+        <v>-6.608253933609414</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.268886097053711</v>
       </c>
       <c r="E37">
-        <v>-27.71889563256004</v>
+        <v>-28.93390332271402</v>
       </c>
       <c r="F37">
-        <v>-1.99764210216203</v>
+        <v>-1.506190774531348</v>
       </c>
       <c r="G37">
-        <v>-5.052870254530251</v>
+        <v>-6.51183760532368</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.78029894148343</v>
       </c>
       <c r="E38">
-        <v>-25.99562107673314</v>
+        <v>-28.24266799323521</v>
       </c>
       <c r="F38">
-        <v>-1.609047498202157</v>
+        <v>-1.27714884439209</v>
       </c>
       <c r="G38">
-        <v>-3.909245608534558</v>
+        <v>-7.116439226615238</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.175937457514844</v>
       </c>
       <c r="E39">
-        <v>-26.16194287008686</v>
+        <v>-27.27854682005417</v>
       </c>
       <c r="F39">
-        <v>-1.612313750871395</v>
+        <v>-1.256543205247453</v>
       </c>
       <c r="G39">
-        <v>-5.69571198734593</v>
+        <v>-7.207704346041866</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.454563691559252</v>
       </c>
       <c r="E40">
-        <v>-23.45507470284595</v>
+        <v>-26.62887835349176</v>
       </c>
       <c r="F40">
-        <v>-1.875715532511374</v>
+        <v>-1.46468873928369</v>
       </c>
       <c r="G40">
-        <v>-5.657912178378531</v>
+        <v>-7.127519622535178</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.620334564867368</v>
       </c>
       <c r="E41">
-        <v>-25.0708704565748</v>
+        <v>-26.53583632653016</v>
       </c>
       <c r="F41">
-        <v>-1.343392557226564</v>
+        <v>-1.241427156881167</v>
       </c>
       <c r="G41">
-        <v>-5.684780565975256</v>
+        <v>-7.68763413287001</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.683263068361185</v>
       </c>
       <c r="E42">
-        <v>-24.23775350796166</v>
+        <v>-25.11724203041334</v>
       </c>
       <c r="F42">
-        <v>-1.38507434820063</v>
+        <v>-0.8537039954290391</v>
       </c>
       <c r="G42">
-        <v>-6.159780950495425</v>
+        <v>-7.503150672148584</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.663335331767047</v>
       </c>
       <c r="E43">
-        <v>-24.0551699644464</v>
+        <v>-24.86621965922016</v>
       </c>
       <c r="F43">
-        <v>-1.074888032385341</v>
+        <v>-1.300908906606589</v>
       </c>
       <c r="G43">
-        <v>-6.290617020752962</v>
+        <v>-7.702769947075558</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.58144311034917</v>
       </c>
       <c r="E44">
-        <v>-21.82596523553455</v>
+        <v>-25.23355588530035</v>
       </c>
       <c r="F44">
-        <v>-0.88836868613399</v>
+        <v>-0.7389949909589747</v>
       </c>
       <c r="G44">
-        <v>-7.083492677408411</v>
+        <v>-8.037270778909058</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.458414664746503</v>
       </c>
       <c r="E45">
-        <v>-22.84538813329726</v>
+        <v>-23.87518123653753</v>
       </c>
       <c r="F45">
-        <v>-0.2090370046091574</v>
+        <v>-0.8041808786200734</v>
       </c>
       <c r="G45">
-        <v>-6.704173680064257</v>
+        <v>-8.036347136703601</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.318936174290544</v>
       </c>
       <c r="E46">
-        <v>-20.38462894295121</v>
+        <v>-23.2799359705993</v>
       </c>
       <c r="F46">
-        <v>-1.327049696736732</v>
+        <v>-0.6790882887559173</v>
       </c>
       <c r="G46">
-        <v>-8.366216515327661</v>
+        <v>-8.36798765719117</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.184066265421399</v>
       </c>
       <c r="E47">
-        <v>-20.89044137571196</v>
+        <v>-22.5934962950946</v>
       </c>
       <c r="F47">
-        <v>-0.5540130946072199</v>
+        <v>-0.9427973947023343</v>
       </c>
       <c r="G47">
-        <v>-8.629957746804779</v>
+        <v>-8.557989797326561</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.068568767962954</v>
       </c>
       <c r="E48">
-        <v>-18.18591895800702</v>
+        <v>-21.69333981727191</v>
       </c>
       <c r="F48">
-        <v>-0.6443763811090067</v>
+        <v>-0.7562175776305792</v>
       </c>
       <c r="G48">
-        <v>-7.423899522483971</v>
+        <v>-8.751418352095099</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.987927122433503</v>
       </c>
       <c r="E49">
-        <v>-17.82834612188736</v>
+        <v>-21.12451819716844</v>
       </c>
       <c r="F49">
-        <v>-0.6676120867575329</v>
+        <v>-0.5662845293122918</v>
       </c>
       <c r="G49">
-        <v>-8.368043936465339</v>
+        <v>-9.039846321658562</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.949087082855538</v>
       </c>
       <c r="E50">
-        <v>-19.78078863334642</v>
+        <v>-20.89405962644409</v>
       </c>
       <c r="F50">
-        <v>-0.9796506320854815</v>
+        <v>-0.2672372699624478</v>
       </c>
       <c r="G50">
-        <v>-8.646821665781825</v>
+        <v>-8.982501051827306</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.953038792828587</v>
       </c>
       <c r="E51">
-        <v>-19.01236999288087</v>
+        <v>-20.26966910179249</v>
       </c>
       <c r="F51">
-        <v>0.05594281693315406</v>
+        <v>-0.4530856386175309</v>
       </c>
       <c r="G51">
-        <v>-7.7688053989474</v>
+        <v>-10.15956551831518</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.002664966313445</v>
       </c>
       <c r="E52">
-        <v>-17.39771088612795</v>
+        <v>-20.14513153810755</v>
       </c>
       <c r="F52">
-        <v>-0.192289072459357</v>
+        <v>-0.70138793923928</v>
       </c>
       <c r="G52">
-        <v>-8.610514912852638</v>
+        <v>-10.20204312812957</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.089214398271718</v>
       </c>
       <c r="E53">
-        <v>-17.28659571940174</v>
+        <v>-18.90445192880408</v>
       </c>
       <c r="F53">
-        <v>-0.3378224563549937</v>
+        <v>-0.4427625240438435</v>
       </c>
       <c r="G53">
-        <v>-8.837691168848506</v>
+        <v>-10.07932782607986</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.204192158100067</v>
       </c>
       <c r="E54">
-        <v>-16.26306549571408</v>
+        <v>-17.99043832051791</v>
       </c>
       <c r="F54">
-        <v>-0.5120322630007438</v>
+        <v>-0.7078235255916293</v>
       </c>
       <c r="G54">
-        <v>-9.140748439150009</v>
+        <v>-9.8759245976015</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.339806082562783</v>
       </c>
       <c r="E55">
-        <v>-16.09643576612784</v>
+        <v>-18.42481407580766</v>
       </c>
       <c r="F55">
-        <v>-0.34202310745459</v>
+        <v>-0.328310313468647</v>
       </c>
       <c r="G55">
-        <v>-9.549428664881958</v>
+        <v>-9.826700095978078</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.479965799917658</v>
       </c>
       <c r="E56">
-        <v>-15.20376032736582</v>
+        <v>-18.03762049120383</v>
       </c>
       <c r="F56">
-        <v>-0.6491759418408272</v>
+        <v>-0.4215289824078838</v>
       </c>
       <c r="G56">
-        <v>-8.951679872856692</v>
+        <v>-10.32995929722147</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.615009930362607</v>
       </c>
       <c r="E57">
-        <v>-13.57777550711972</v>
+        <v>-17.01803456837685</v>
       </c>
       <c r="F57">
-        <v>-0.5464534136892716</v>
+        <v>-0.1198301190016786</v>
       </c>
       <c r="G57">
-        <v>-9.510970057352244</v>
+        <v>-10.70794414471329</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.734794721419139</v>
       </c>
       <c r="E58">
-        <v>-13.61725474351859</v>
+        <v>-17.69017332296533</v>
       </c>
       <c r="F58">
-        <v>-0.2484001952227871</v>
+        <v>-0.4218296797751</v>
       </c>
       <c r="G58">
-        <v>-9.305391800454583</v>
+        <v>-10.45819658923067</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.827291052779648</v>
       </c>
       <c r="E59">
-        <v>-13.5323639697708</v>
+        <v>-17.09296269930777</v>
       </c>
       <c r="F59">
-        <v>-0.4975764234544896</v>
+        <v>-0.3264067251770137</v>
       </c>
       <c r="G59">
-        <v>-9.51317157013586</v>
+        <v>-10.65378693023635</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.887969544942139</v>
       </c>
       <c r="E60">
-        <v>-13.77059340189231</v>
+        <v>-16.55958997373633</v>
       </c>
       <c r="F60">
-        <v>-0.5551620401949028</v>
+        <v>-0.539114078500468</v>
       </c>
       <c r="G60">
-        <v>-9.701773349508139</v>
+        <v>-10.88247610554367</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.910781380869984</v>
       </c>
       <c r="E61">
-        <v>-14.03333093534334</v>
+        <v>-16.97309399232473</v>
       </c>
       <c r="F61">
-        <v>0.3643266052799512</v>
+        <v>-0.4080622135405722</v>
       </c>
       <c r="G61">
-        <v>-10.46343718281934</v>
+        <v>-11.03882655027237</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.891277324329522</v>
       </c>
       <c r="E62">
-        <v>-12.44406298235143</v>
+        <v>-15.86991696779016</v>
       </c>
       <c r="F62">
-        <v>-0.7866219747829323</v>
+        <v>-0.3818419001397594</v>
       </c>
       <c r="G62">
-        <v>-10.10940413230414</v>
+        <v>-10.72886017143041</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.830902423576726</v>
       </c>
       <c r="E63">
-        <v>-13.22189632027893</v>
+        <v>-15.87718064009847</v>
       </c>
       <c r="F63">
-        <v>-0.7809435162367416</v>
+        <v>-0.2209729505160955</v>
       </c>
       <c r="G63">
-        <v>-11.20930971390822</v>
+        <v>-10.59941453029936</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.727643488811677</v>
       </c>
       <c r="E64">
-        <v>-12.29210550855004</v>
+        <v>-15.36168180143531</v>
       </c>
       <c r="F64">
-        <v>-0.5506847143827714</v>
+        <v>-0.7873882146305218</v>
       </c>
       <c r="G64">
-        <v>-9.964819366422009</v>
+        <v>-10.57082796956776</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.582377242893302</v>
       </c>
       <c r="E65">
-        <v>-12.92707907695756</v>
+        <v>-15.88219366082496</v>
       </c>
       <c r="F65">
-        <v>-0.1491609520000035</v>
+        <v>-0.6594551529421662</v>
       </c>
       <c r="G65">
-        <v>-9.277894409205397</v>
+        <v>-10.52976727324418</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.399310017540917</v>
       </c>
       <c r="E66">
-        <v>-11.27723825563906</v>
+        <v>-15.11494789512739</v>
       </c>
       <c r="F66">
-        <v>-0.629654635626454</v>
+        <v>-0.8827059665684526</v>
       </c>
       <c r="G66">
-        <v>-9.218453564047781</v>
+        <v>-10.42839505828615</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.179627621783564</v>
       </c>
       <c r="E67">
-        <v>-12.31173644337329</v>
+        <v>-14.58551494194263</v>
       </c>
       <c r="F67">
-        <v>-0.9691444483157754</v>
+        <v>-0.6375141855442157</v>
       </c>
       <c r="G67">
-        <v>-10.84965535706733</v>
+        <v>-10.33131331034703</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.927733673453874</v>
       </c>
       <c r="E68">
-        <v>-12.38183269253802</v>
+        <v>-15.64739228352725</v>
       </c>
       <c r="F68">
-        <v>-0.6047149782303692</v>
+        <v>-0.8857444182019211</v>
       </c>
       <c r="G68">
-        <v>-10.21381542806721</v>
+        <v>-10.28487628806767</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.649427033172098</v>
       </c>
       <c r="E69">
-        <v>-11.05548341195744</v>
+        <v>-15.15526037074367</v>
       </c>
       <c r="F69">
-        <v>-0.2399947511865805</v>
+        <v>-0.5120943905559537</v>
       </c>
       <c r="G69">
-        <v>-10.78036894947593</v>
+        <v>-10.82645174338258</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.347184424073816</v>
       </c>
       <c r="E70">
-        <v>-12.0255187721925</v>
+        <v>-14.86165222998236</v>
       </c>
       <c r="F70">
-        <v>-0.3797742951023719</v>
+        <v>-0.7554281434957113</v>
       </c>
       <c r="G70">
-        <v>-10.77888913561987</v>
+        <v>-10.16038984415446</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.026893934752039</v>
       </c>
       <c r="E71">
-        <v>-11.40600088557315</v>
+        <v>-16.15748865269925</v>
       </c>
       <c r="F71">
-        <v>-0.6768400996247194</v>
+        <v>-0.9950574374101495</v>
       </c>
       <c r="G71">
-        <v>-9.460537206606988</v>
+        <v>-10.3399770080233</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.69363866253274</v>
       </c>
       <c r="E72">
-        <v>-13.19012907511512</v>
+        <v>-15.0086238539013</v>
       </c>
       <c r="F72">
-        <v>-0.8768419537240348</v>
+        <v>-0.8223602296419114</v>
       </c>
       <c r="G72">
-        <v>-9.696830705018007</v>
+        <v>-10.56515038396791</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.348235562188644</v>
       </c>
       <c r="E73">
-        <v>-12.04695656814481</v>
+        <v>-15.40332564840985</v>
       </c>
       <c r="F73">
-        <v>-0.9943301308304915</v>
+        <v>-0.816585680476996</v>
       </c>
       <c r="G73">
-        <v>-8.965713275397663</v>
+        <v>-10.03851542067173</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.9968452420176266</v>
       </c>
       <c r="E74">
-        <v>-11.7652175577576</v>
+        <v>-15.41057573529613</v>
       </c>
       <c r="F74">
-        <v>-1.176879940487627</v>
+        <v>-0.9203850862521908</v>
       </c>
       <c r="G74">
-        <v>-8.786364470807646</v>
+        <v>-9.434638808853268</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.6434049292545709</v>
       </c>
       <c r="E75">
-        <v>-12.19223907125889</v>
+        <v>-15.0956475389067</v>
       </c>
       <c r="F75">
-        <v>-1.327323886347059</v>
+        <v>-0.6409858733293484</v>
       </c>
       <c r="G75">
-        <v>-9.02214152411454</v>
+        <v>-9.340960301728511</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.2888610644233805</v>
       </c>
       <c r="E76">
-        <v>-11.9066191586471</v>
+        <v>-15.63045126226455</v>
       </c>
       <c r="F76">
-        <v>-1.182245276155559</v>
+        <v>-0.7339866816416489</v>
       </c>
       <c r="G76">
-        <v>-7.74100674805414</v>
+        <v>-9.715677640773078</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.06156511691103264</v>
       </c>
       <c r="E77">
-        <v>-14.12160900764887</v>
+        <v>-16.19335869531401</v>
       </c>
       <c r="F77">
-        <v>-1.148888577579629</v>
+        <v>-1.239752197992707</v>
       </c>
       <c r="G77">
-        <v>-8.25293295751934</v>
+        <v>-9.042938371192241</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.4058745774508139</v>
       </c>
       <c r="E78">
-        <v>-13.20415375911688</v>
+        <v>-16.80013345607577</v>
       </c>
       <c r="F78">
-        <v>-0.9618771810910153</v>
+        <v>-1.443591878269192</v>
       </c>
       <c r="G78">
-        <v>-7.657494926280485</v>
+        <v>-9.330846585106039</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.7414228193445677</v>
       </c>
       <c r="E79">
-        <v>-14.33278080757455</v>
+        <v>-16.27369382421008</v>
       </c>
       <c r="F79">
-        <v>-1.074471363581732</v>
+        <v>-1.324076686128085</v>
       </c>
       <c r="G79">
-        <v>-7.670955604443161</v>
+        <v>-8.708030342257411</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.062142980939946</v>
       </c>
       <c r="E80">
-        <v>-14.96805778374059</v>
+        <v>-17.20372464506137</v>
       </c>
       <c r="F80">
-        <v>-1.303165379411814</v>
+        <v>-1.158577991090175</v>
       </c>
       <c r="G80">
-        <v>-7.577677673328656</v>
+        <v>-9.080811012161504</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.36434506760079</v>
       </c>
       <c r="E81">
-        <v>-16.62943715683064</v>
+        <v>-18.24670013613797</v>
       </c>
       <c r="F81">
-        <v>-1.778162016953287</v>
+        <v>-1.436934289452892</v>
       </c>
       <c r="G81">
-        <v>-6.890554083379686</v>
+        <v>-7.708768655592717</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.641117713082866</v>
       </c>
       <c r="E82">
-        <v>-15.50922401307922</v>
+        <v>-18.32644203493904</v>
       </c>
       <c r="F82">
-        <v>-1.376752569272106</v>
+        <v>-1.434031690073483</v>
       </c>
       <c r="G82">
-        <v>-6.608839900169865</v>
+        <v>-8.17861783125378</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.884297981948401</v>
       </c>
       <c r="E83">
-        <v>-16.80380604849599</v>
+        <v>-19.24341726522622</v>
       </c>
       <c r="F83">
-        <v>-1.393586651631797</v>
+        <v>-1.463387374093892</v>
       </c>
       <c r="G83">
-        <v>-5.3467175871415</v>
+        <v>-7.584103442220382</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.087809346533907</v>
       </c>
       <c r="E84">
-        <v>-17.14601377230762</v>
+        <v>-19.44939490546511</v>
       </c>
       <c r="F84">
-        <v>-1.353008246038261</v>
+        <v>-1.233159221833825</v>
       </c>
       <c r="G84">
-        <v>-5.867896771388963</v>
+        <v>-7.906004337731416</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.243105962590092</v>
       </c>
       <c r="E85">
-        <v>-18.89462966868144</v>
+        <v>-20.83584156460148</v>
       </c>
       <c r="F85">
-        <v>-1.498491099522327</v>
+        <v>-2.079648818304376</v>
       </c>
       <c r="G85">
-        <v>-5.720501352343992</v>
+        <v>-7.111410507941085</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.34367977643436</v>
       </c>
       <c r="E86">
-        <v>-18.17615556804648</v>
+        <v>-21.13585749608364</v>
       </c>
       <c r="F86">
-        <v>-1.449520503771028</v>
+        <v>-1.825979525279889</v>
       </c>
       <c r="G86">
-        <v>-5.840634428873065</v>
+        <v>-7.006257649977214</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.384490961442914</v>
       </c>
       <c r="E87">
-        <v>-21.13424988781092</v>
+        <v>-22.78343860887233</v>
       </c>
       <c r="F87">
-        <v>-1.752701316460842</v>
+        <v>-1.988043809065792</v>
       </c>
       <c r="G87">
-        <v>-5.604105881728756</v>
+        <v>-6.302468773783553</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.361875286033108</v>
       </c>
       <c r="E88">
-        <v>-21.58813430912571</v>
+        <v>-24.72090092831401</v>
       </c>
       <c r="F88">
-        <v>-2.14847289559857</v>
+        <v>-1.860495109852336</v>
       </c>
       <c r="G88">
-        <v>-5.401262135446532</v>
+        <v>-6.707232624142544</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.274432500659546</v>
       </c>
       <c r="E89">
-        <v>-23.52150288806447</v>
+        <v>-25.15221090670057</v>
       </c>
       <c r="F89">
-        <v>-1.780461564863459</v>
+        <v>-2.041972183722846</v>
       </c>
       <c r="G89">
-        <v>-5.347197616244695</v>
+        <v>-6.059050981372021</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.122319633343154</v>
       </c>
       <c r="E90">
-        <v>-25.63907620421323</v>
+        <v>-25.47188494385004</v>
       </c>
       <c r="F90">
-        <v>-2.411451381495718</v>
+        <v>-2.445624021963406</v>
       </c>
       <c r="G90">
-        <v>-5.94763126070231</v>
+        <v>-6.571202307933891</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.909393817111708</v>
       </c>
       <c r="E91">
-        <v>-26.07981446548375</v>
+        <v>-28.01110900332699</v>
       </c>
       <c r="F91">
-        <v>-3.058695423305709</v>
+        <v>-2.248312705188383</v>
       </c>
       <c r="G91">
-        <v>-3.737590511777808</v>
+        <v>-6.074749588319245</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.6392071830482</v>
       </c>
       <c r="E92">
-        <v>-28.59218014562121</v>
+        <v>-28.85345045349375</v>
       </c>
       <c r="F92">
-        <v>-3.008734100140662</v>
+        <v>-2.61416282536959</v>
       </c>
       <c r="G92">
-        <v>-5.108801921416237</v>
+        <v>-6.111774729630453</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.317414655682568</v>
       </c>
       <c r="E93">
-        <v>-27.94729827608491</v>
+        <v>-29.5895154114115</v>
       </c>
       <c r="F93">
-        <v>-2.41648537020253</v>
+        <v>-2.559046571856923</v>
       </c>
       <c r="G93">
-        <v>-6.036641898616694</v>
+        <v>-6.144317392281489</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.9523622705709499</v>
       </c>
       <c r="E94">
-        <v>-29.54381178748909</v>
+        <v>-32.20487670437942</v>
       </c>
       <c r="F94">
-        <v>-3.330751987570136</v>
+        <v>-2.91031494064665</v>
       </c>
       <c r="G94">
-        <v>-4.691305712913208</v>
+        <v>-6.709288472922432</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.5497280462586396</v>
       </c>
       <c r="E95">
-        <v>-32.5701388893641</v>
+        <v>-33.8513958900133</v>
       </c>
       <c r="F95">
-        <v>-3.807123715000257</v>
+        <v>-2.812706752839979</v>
       </c>
       <c r="G95">
-        <v>-4.724536969036413</v>
+        <v>-7.28504200038478</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.1158728566123059</v>
       </c>
       <c r="E96">
-        <v>-36.17819602650145</v>
+        <v>-35.46566554800156</v>
       </c>
       <c r="F96">
-        <v>-3.342412087131942</v>
+        <v>-3.209104577734223</v>
       </c>
       <c r="G96">
-        <v>-6.554152998406645</v>
+        <v>-7.034364181605627</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.3358593064581175</v>
       </c>
       <c r="E97">
-        <v>-35.75734455883561</v>
+        <v>-37.78272720113622</v>
       </c>
       <c r="F97">
-        <v>-4.016245894204395</v>
+        <v>-3.728687262363977</v>
       </c>
       <c r="G97">
-        <v>-5.656935567444446</v>
+        <v>-7.309563211194162</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.8074435869600997</v>
       </c>
       <c r="E98">
-        <v>-38.4871675608214</v>
+        <v>-40.61024750136349</v>
       </c>
       <c r="F98">
-        <v>-3.789783500157454</v>
+        <v>-3.394596748406102</v>
       </c>
       <c r="G98">
-        <v>-5.896599201214444</v>
+        <v>-7.779197201395172</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.275212662487167</v>
       </c>
       <c r="E99">
-        <v>-40.85776936214874</v>
+        <v>-41.15091559856128</v>
       </c>
       <c r="F99">
-        <v>-5.016323090828001</v>
+        <v>-3.858469240095381</v>
       </c>
       <c r="G99">
-        <v>-6.003102761758337</v>
+        <v>-7.238462624647235</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.753110068018069</v>
       </c>
       <c r="E100">
-        <v>-43.13328000202602</v>
+        <v>-43.95211867209297</v>
       </c>
       <c r="F100">
-        <v>-4.741626519650851</v>
+        <v>-4.024792160699077</v>
       </c>
       <c r="G100">
-        <v>-4.761820332899685</v>
+        <v>-8.045616664213561</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.198947042467996</v>
       </c>
       <c r="E101">
-        <v>-43.99454820930784</v>
+        <v>-45.8311568841247</v>
       </c>
       <c r="F101">
-        <v>-4.804324820001344</v>
+        <v>-4.487381511281419</v>
       </c>
       <c r="G101">
-        <v>-5.426720230643528</v>
+        <v>-7.920524390466659</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.661993861236197</v>
       </c>
       <c r="E102">
-        <v>-47.51442463633083</v>
+        <v>-48.7146049704652</v>
       </c>
       <c r="F102">
-        <v>-4.856129260637618</v>
+        <v>-4.837022966492048</v>
       </c>
       <c r="G102">
-        <v>-7.796114089100848</v>
+        <v>-8.596071002664798</v>
       </c>
     </row>
   </sheetData>
